--- a/owlcms/src/main/resources/templates/competitionBook/Score-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/competitionBook/Score-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\competitionBook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56360159-9D28-45CD-B052-CC9A1713B91D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4E0AC0-3E38-400B-B193-5AA906974F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C" sheetId="35" r:id="rId1"/>
@@ -513,7 +513,7 @@
     <t>${l.categoryScoreRank &lt; 0 ? t.get("Results.Extra/Invited") : (l.categoryScoreRank &gt; 0 ? l.categoryScoreRank : "" )}</t>
   </si>
   <si>
-    <t>${l.categoryScoreRank}</t>
+    <t>${l.categoryScoreRank &lt; 0 ? 0 : l.categoryScoreRank}</t>
   </si>
 </sst>
 </file>
@@ -1489,10 +1489,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1548,6 +1544,10 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -1611,47 +1611,7 @@
     <cellStyle name="Titre 1 1 1" xfId="9" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
     <cellStyle name="Titre de la feuille" xfId="10" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="34"/>
-          <bgColor indexed="13"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -5513,59 +5473,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="112" t="s">
+      <c r="B1" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="114" t="s">
+      <c r="C1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="118" t="s">
+      <c r="E1" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="118" t="s">
+      <c r="G1" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="118" t="s">
+      <c r="H1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="120" t="s">
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="106" t="s">
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="105" t="s">
         <v>139</v>
       </c>
-      <c r="T1" s="107"/>
-      <c r="U1" s="108"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:24" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="111"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
       <c r="I2" s="32">
         <v>1</v>
       </c>
@@ -5801,11 +5761,11 @@
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1"/>
-      <c r="R15" s="109"/>
+      <c r="R15" s="108"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C16" s="1"/>
-      <c r="R16" s="109"/>
+      <c r="R16" s="108"/>
     </row>
     <row r="17" spans="3:3" x14ac:dyDescent="0.2">
       <c r="C17" s="1"/>
@@ -6096,21 +6056,13 @@
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="N1:R1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B8:C8">
-    <cfRule type="expression" dxfId="12" priority="4" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:C9">
-    <cfRule type="expression" dxfId="11" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="B8:C9">
+    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:D4">
-    <cfRule type="expression" dxfId="10" priority="2" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="9" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6166,59 +6118,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="110" t="s">
+      <c r="A1" s="109" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="112" t="s">
+      <c r="B1" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="C1" s="114" t="s">
+      <c r="C1" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="118" t="s">
+      <c r="E1" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="118" t="s">
+      <c r="F1" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="118" t="s">
+      <c r="G1" s="117" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="118" t="s">
+      <c r="H1" s="117" t="s">
         <v>43</v>
       </c>
-      <c r="I1" s="120" t="s">
+      <c r="I1" s="119" t="s">
         <v>44</v>
       </c>
-      <c r="J1" s="121"/>
-      <c r="K1" s="121"/>
-      <c r="L1" s="121"/>
-      <c r="M1" s="121"/>
-      <c r="N1" s="120" t="s">
+      <c r="J1" s="120"/>
+      <c r="K1" s="120"/>
+      <c r="L1" s="120"/>
+      <c r="M1" s="120"/>
+      <c r="N1" s="119" t="s">
         <v>45</v>
       </c>
-      <c r="O1" s="121"/>
-      <c r="P1" s="121"/>
-      <c r="Q1" s="121"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="106" t="s">
+      <c r="O1" s="120"/>
+      <c r="P1" s="120"/>
+      <c r="Q1" s="120"/>
+      <c r="R1" s="120"/>
+      <c r="S1" s="105" t="s">
         <v>139</v>
       </c>
-      <c r="T1" s="107"/>
-      <c r="U1" s="108"/>
+      <c r="T1" s="106"/>
+      <c r="U1" s="107"/>
     </row>
     <row r="2" spans="1:23" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="111"/>
-      <c r="B2" s="113"/>
-      <c r="C2" s="115"/>
-      <c r="D2" s="117"/>
-      <c r="E2" s="119"/>
-      <c r="F2" s="119"/>
-      <c r="G2" s="119"/>
-      <c r="H2" s="119"/>
+      <c r="A2" s="110"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="114"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
       <c r="I2" s="32">
         <v>1</v>
       </c>
@@ -6455,11 +6407,11 @@
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C16" s="1"/>
-      <c r="P16" s="109"/>
+      <c r="P16" s="108"/>
     </row>
     <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1"/>
-      <c r="P17" s="109"/>
+      <c r="P17" s="108"/>
     </row>
     <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1"/>
@@ -6750,21 +6702,13 @@
     <mergeCell ref="I1:M1"/>
     <mergeCell ref="N1:R1"/>
   </mergeCells>
-  <conditionalFormatting sqref="B8:C8">
-    <cfRule type="expression" dxfId="8" priority="4" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B9:C9">
-    <cfRule type="expression" dxfId="7" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="B8:C9">
+    <cfRule type="expression" dxfId="5" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3:D4">
-    <cfRule type="expression" dxfId="6" priority="2" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="2" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -6825,10 +6769,10 @@
       <c r="C1" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="118" t="s">
+      <c r="E1" s="117" t="s">
         <v>40</v>
       </c>
       <c r="F1" s="127" t="s">
@@ -6855,10 +6799,10 @@
       <c r="Q1" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="105" t="s">
+      <c r="R1" s="121" t="s">
         <v>140</v>
       </c>
-      <c r="S1" s="105"/>
+      <c r="S1" s="121"/>
       <c r="U1"/>
       <c r="V1"/>
     </row>
@@ -6867,7 +6811,7 @@
       <c r="B2" s="123"/>
       <c r="C2" s="125"/>
       <c r="D2" s="126"/>
-      <c r="E2" s="118"/>
+      <c r="E2" s="117"/>
       <c r="F2" s="127"/>
       <c r="G2" s="128"/>
       <c r="H2" s="130"/>
@@ -7316,7 +7260,7 @@
     <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
       <formula>AND(("$'Hommes Sinclair'.$#REF!$#REF!"),"$'Hommes Sinclair'.$#REF!$#REF!","$'Hommes Sinclair'.$#REF!$#REF!")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7371,10 +7315,10 @@
       <c r="C1" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="116" t="s">
+      <c r="D1" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="118" t="s">
+      <c r="E1" s="117" t="s">
         <v>40</v>
       </c>
       <c r="F1" s="127" t="s">
@@ -7401,17 +7345,17 @@
       <c r="Q1" s="132" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="105" t="s">
+      <c r="R1" s="121" t="s">
         <v>140</v>
       </c>
-      <c r="S1" s="105"/>
+      <c r="S1" s="121"/>
     </row>
     <row r="2" spans="1:19" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="123"/>
       <c r="B2" s="123"/>
       <c r="C2" s="125"/>
       <c r="D2" s="126"/>
-      <c r="E2" s="118"/>
+      <c r="E2" s="117"/>
       <c r="F2" s="127"/>
       <c r="G2" s="128"/>
       <c r="H2" s="130"/>
@@ -7835,7 +7779,7 @@
     <mergeCell ref="Q1:Q2"/>
   </mergeCells>
   <conditionalFormatting sqref="B4:C4">
-    <cfRule type="expression" dxfId="3" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
       <formula>AND(("$'Hommes Sinclair'.$#REF!$#REF!"),"$'Hommes Sinclair'.$#REF!$#REF!","$'Hommes Sinclair'.$#REF!$#REF!")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9165,10 +9109,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C5:D5">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
       <formula>AND((#REF!),#REF!,#REF!)</formula>
     </cfRule>
   </conditionalFormatting>

--- a/owlcms/src/main/resources/templates/competitionBook/Score-LETTER.xlsx
+++ b/owlcms/src/main/resources/templates/competitionBook/Score-LETTER.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\competitionBook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4E0AC0-3E38-400B-B193-5AA906974F81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85DB95F-CB2B-4BDF-A3F8-F240138018F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="447" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="1875" windowWidth="21600" windowHeight="12105" tabRatio="447" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="C" sheetId="35" r:id="rId1"/>
@@ -141,9 +141,6 @@
     <t>${t.get("Lot")}</t>
   </si>
   <si>
-    <t>${t.get("Results.MenPerTeam")}</t>
-  </si>
-  <si>
     <t>${t.get("Results.Teams")}</t>
   </si>
   <si>
@@ -159,9 +156,6 @@
     <t>${t.get("Gender.M")}</t>
   </si>
   <si>
-    <t>${t.get("Results.WomenPerTeam")}</t>
-  </si>
-  <si>
     <t>${t.get("Gender.F")}</t>
   </si>
   <si>
@@ -306,12 +300,6 @@
     <t>${group.weighInShortDateTime != "" ? (t.get("WeighInTime")+': '+group.weighInShortDateTime) : ""}</t>
   </si>
   <si>
-    <t>${competition.menPerTeamElseDefault}</t>
-  </si>
-  <si>
-    <t>${competition.womenPerTeamElseDefault}</t>
-  </si>
-  <si>
     <t>${group.item.category}</t>
   </si>
   <si>
@@ -514,6 +502,18 @@
   </si>
   <si>
     <t>${l.categoryScoreRank &lt; 0 ? 0 : l.categoryScoreRank}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.MenBestN")}</t>
+  </si>
+  <si>
+    <t>${competition.menBestNElseDefault}</t>
+  </si>
+  <si>
+    <t>${t.get("Results.WomenBestN")}</t>
+  </si>
+  <si>
+    <t>${competition.womenBestNElseDefault}</t>
   </si>
 </sst>
 </file>
@@ -2120,10 +2120,10 @@
   <sheetData>
     <row r="1" spans="1:19" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B1" s="103" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C1" s="103"/>
       <c r="D1" s="103"/>
@@ -2133,18 +2133,18 @@
       <c r="H1" s="39"/>
       <c r="I1" s="39"/>
       <c r="J1" s="39" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="K1" s="40" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="39" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B2" s="104" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C2" s="104"/>
       <c r="D2" s="104"/>
@@ -2154,18 +2154,18 @@
       <c r="H2" s="39"/>
       <c r="I2" s="39"/>
       <c r="J2" s="39" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K2" s="40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="39" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" s="104" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C3" s="104"/>
       <c r="D3" s="104"/>
@@ -2192,24 +2192,24 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:19" s="3" customFormat="1" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B8" s="43"/>
       <c r="C8" s="43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D8" s="40" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G8" s="43"/>
       <c r="H8" s="43"/>
       <c r="I8" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J8" s="43"/>
       <c r="L8" s="44"/>
@@ -2234,42 +2234,42 @@
     </row>
     <row r="10" spans="1:19" s="40" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C10" s="39" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="40" t="s">
+      <c r="I10" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="39" t="s">
+      <c r="L10" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="40" t="s">
+      <c r="M10" s="40" t="s">
         <v>68</v>
-      </c>
-      <c r="L10" s="39" t="s">
-        <v>69</v>
-      </c>
-      <c r="M10" s="40" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="39" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E11" s="1"/>
       <c r="H11" s="39" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I11" s="40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J11" s="40"/>
       <c r="K11" s="1"/>
       <c r="M11" s="40" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="N11" s="1"/>
       <c r="P11"/>
@@ -2279,22 +2279,22 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="39" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E12" s="1"/>
       <c r="H12" s="39" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J12" s="40"/>
       <c r="K12" s="1"/>
       <c r="M12" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="40"/>
@@ -2304,15 +2304,15 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D13" s="47" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="M13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="N13"/>
       <c r="S13"/>
@@ -2325,7 +2325,7 @@
       <c r="K14" s="40"/>
       <c r="L14" s="40"/>
       <c r="M14" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="N14" s="40"/>
       <c r="O14" s="40"/>
@@ -3816,10 +3816,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5486,33 +5486,33 @@
         <v>16</v>
       </c>
       <c r="E1" s="117" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="117" t="s">
+      <c r="H1" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="117" t="s">
+      <c r="I1" s="119" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="117" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="119" t="s">
-        <v>44</v>
       </c>
       <c r="J1" s="120"/>
       <c r="K1" s="120"/>
       <c r="L1" s="120"/>
       <c r="M1" s="120"/>
       <c r="N1" s="119" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O1" s="120"/>
       <c r="P1" s="120"/>
       <c r="Q1" s="120"/>
       <c r="R1" s="120"/>
       <c r="S1" s="105" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="T1" s="106"/>
       <c r="U1" s="107"/>
@@ -5536,10 +5536,10 @@
         <v>3</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M2" s="51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N2" s="16">
         <v>1</v>
@@ -5551,24 +5551,24 @@
         <v>3</v>
       </c>
       <c r="Q2" s="31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R2" s="51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S2" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="U2" s="51" t="s">
         <v>46</v>
-      </c>
-      <c r="T2" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="U2" s="51" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:24" s="18" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="52" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="5" spans="1:24" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="56" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B5" s="57"/>
       <c r="C5" s="58"/>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -5678,7 +5678,7 @@
         <v>22</v>
       </c>
       <c r="M7" s="50" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N7" s="24" t="s">
         <v>23</v>
@@ -5693,16 +5693,16 @@
         <v>26</v>
       </c>
       <c r="R7" s="50" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="S7" s="23" t="s">
         <v>4</v>
       </c>
       <c r="T7" s="22" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="U7" s="49" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.2">
@@ -6131,33 +6131,33 @@
         <v>16</v>
       </c>
       <c r="E1" s="117" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="117" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="117" t="s">
+      <c r="H1" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="117" t="s">
+      <c r="I1" s="119" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="117" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="119" t="s">
-        <v>44</v>
       </c>
       <c r="J1" s="120"/>
       <c r="K1" s="120"/>
       <c r="L1" s="120"/>
       <c r="M1" s="120"/>
       <c r="N1" s="119" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="O1" s="120"/>
       <c r="P1" s="120"/>
       <c r="Q1" s="120"/>
       <c r="R1" s="120"/>
       <c r="S1" s="105" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="T1" s="106"/>
       <c r="U1" s="107"/>
@@ -6181,10 +6181,10 @@
         <v>3</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M2" s="51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N2" s="16">
         <v>1</v>
@@ -6196,24 +6196,24 @@
         <v>3</v>
       </c>
       <c r="Q2" s="31" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="R2" s="51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="S2" s="60" t="s">
+        <v>44</v>
+      </c>
+      <c r="T2" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="U2" s="51" t="s">
         <v>46</v>
-      </c>
-      <c r="T2" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="U2" s="51" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:23" s="18" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="52" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B3" s="53"/>
       <c r="C3" s="53"/>
@@ -6241,7 +6241,7 @@
     </row>
     <row r="5" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="56" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B5" s="57"/>
       <c r="C5" s="58"/>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D6"/>
       <c r="E6"/>
@@ -6321,7 +6321,7 @@
         <v>22</v>
       </c>
       <c r="M7" s="50" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="N7" s="24" t="s">
         <v>23</v>
@@ -6336,16 +6336,16 @@
         <v>26</v>
       </c>
       <c r="R7" s="50" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="S7" s="23" t="s">
         <v>4</v>
       </c>
       <c r="T7" s="22" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="U7" s="49" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.2">
@@ -6773,34 +6773,34 @@
         <v>16</v>
       </c>
       <c r="E1" s="117" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="127" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="128" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="127" t="s">
+      <c r="H1" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="128" t="s">
+      <c r="I1" s="131" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="129" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="131" t="s">
-        <v>44</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="131"/>
       <c r="L1" s="131"/>
       <c r="M1" s="131" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N1" s="131"/>
       <c r="O1" s="131"/>
       <c r="P1" s="131"/>
       <c r="Q1" s="132" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R1" s="121" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="S1" s="121"/>
       <c r="U1"/>
@@ -6825,7 +6825,7 @@
         <v>3</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M2" s="16">
         <v>1</v>
@@ -6837,19 +6837,19 @@
         <v>3</v>
       </c>
       <c r="P2" s="96" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Q2" s="133"/>
       <c r="R2" s="30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="S2" s="51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="26" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>2</v>
@@ -6920,13 +6920,13 @@
         <v>4</v>
       </c>
       <c r="R4" s="99" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="S4" s="100" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="V4" s="101" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
@@ -7319,34 +7319,34 @@
         <v>16</v>
       </c>
       <c r="E1" s="117" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="127" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="128" t="s">
         <v>40</v>
       </c>
-      <c r="F1" s="127" t="s">
+      <c r="H1" s="129" t="s">
         <v>41</v>
       </c>
-      <c r="G1" s="128" t="s">
+      <c r="I1" s="131" t="s">
         <v>42</v>
-      </c>
-      <c r="H1" s="129" t="s">
-        <v>43</v>
-      </c>
-      <c r="I1" s="131" t="s">
-        <v>44</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="131"/>
       <c r="L1" s="131"/>
       <c r="M1" s="131" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="N1" s="131"/>
       <c r="O1" s="131"/>
       <c r="P1" s="131"/>
       <c r="Q1" s="132" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="R1" s="121" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="S1" s="121"/>
     </row>
@@ -7369,7 +7369,7 @@
         <v>3</v>
       </c>
       <c r="L2" s="31" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M2" s="16">
         <v>1</v>
@@ -7381,19 +7381,19 @@
         <v>3</v>
       </c>
       <c r="P2" s="96" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="Q2" s="133"/>
       <c r="R2" s="30" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="S2" s="51" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D3"/>
       <c r="E3"/>
@@ -7422,7 +7422,7 @@
       </c>
       <c r="D4" s="17"/>
       <c r="E4" s="26" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>2</v>
@@ -7461,10 +7461,10 @@
         <v>4</v>
       </c>
       <c r="R4" s="99" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="S4" s="100" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.2">
@@ -7821,7 +7821,7 @@
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -7832,28 +7832,28 @@
     </row>
     <row r="3" spans="1:18" s="6" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M3" s="38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N3" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O3" s="64" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P3" s="64" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.2">
@@ -7874,7 +7874,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>11</v>
@@ -7886,13 +7886,13 @@
         <v>9</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="P5" s="102" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -7915,7 +7915,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -7923,7 +7923,7 @@
     <row r="9" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:18" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="63" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>29</v>
@@ -7932,48 +7932,48 @@
         <v>28</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L10" s="33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O10" s="33" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P10" s="64" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L11"/>
       <c r="M11"/>
@@ -8006,31 +8006,31 @@
         <v>4</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L12" s="62" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M12" s="62" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N12" s="62" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="O12" s="62" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="P12" s="62" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8069,7 +8069,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>12</v>
@@ -8077,7 +8077,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
@@ -8086,10 +8086,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>
@@ -8134,7 +8134,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8153,28 +8153,28 @@
     </row>
     <row r="3" spans="1:19" s="6" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3" s="64" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="M3" s="38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N3" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O3" s="64" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P3" s="64" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -8197,7 +8197,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C5" s="35" t="s">
         <v>11</v>
@@ -8213,13 +8213,13 @@
         <v>9</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="P5" s="102" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8248,7 +8248,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -8265,7 +8265,7 @@
     </row>
     <row r="10" spans="1:19" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="63" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>29</v>
@@ -8274,48 +8274,48 @@
         <v>28</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L10" s="33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O10" s="33" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P10" s="64" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
@@ -8350,31 +8350,31 @@
         <v>4</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L12" s="62" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M12" s="62" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N12" s="62" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="O12" s="62" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="P12" s="62" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8421,7 +8421,7 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
         <v>13</v>
@@ -8437,7 +8437,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
@@ -8464,10 +8464,10 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
@@ -8520,7 +8520,7 @@
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -8539,31 +8539,31 @@
     </row>
     <row r="3" spans="1:19" s="6" customFormat="1" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B3" s="37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="64" t="s">
-        <v>38</v>
-      </c>
       <c r="M3" s="38" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="N3" s="37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O3" s="64" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P3" s="64" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
@@ -8586,10 +8586,10 @@
         <v>9</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D5" s="35" t="s">
         <v>14</v>
@@ -8605,13 +8605,13 @@
         <v>9</v>
       </c>
       <c r="N5" s="35" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="O5" s="35" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="P5" s="102" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8641,7 +8641,7 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -8658,7 +8658,7 @@
     </row>
     <row r="10" spans="1:19" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="63" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" s="34" t="s">
         <v>29</v>
@@ -8667,48 +8667,48 @@
         <v>28</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F10" s="34" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H10" s="7" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L10" s="33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="N10" s="33" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="O10" s="33" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="P10" s="64" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="H11"/>
       <c r="I11"/>
@@ -8743,31 +8743,31 @@
         <v>4</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="J12" s="10" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="L12" s="62" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M12" s="62" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="N12" s="62" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="O12" s="62" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="P12" s="62" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:19" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
@@ -8814,10 +8814,10 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H15"/>
       <c r="I15"/>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" t="s">
@@ -8847,10 +8847,10 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>153</v>
       </c>
       <c r="H17"/>
       <c r="I17"/>
@@ -8863,10 +8863,10 @@
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="H18"/>
       <c r="I18"/>
@@ -8924,13 +8924,13 @@
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="J1" s="1"/>
     </row>
     <row r="2" spans="1:24" s="65" customFormat="1" ht="15" x14ac:dyDescent="0.25">
       <c r="A2" s="65" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="J2" s="66"/>
     </row>
@@ -8960,54 +8960,54 @@
     </row>
     <row r="4" spans="1:24" s="78" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A4" s="69" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B4" s="70"/>
       <c r="C4" s="71"/>
       <c r="D4" s="72" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E4" s="73" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="F4" s="72" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G4" s="74" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="H4" s="75"/>
       <c r="I4" s="72" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="J4" s="69" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="K4" s="76"/>
       <c r="L4" s="70"/>
       <c r="M4" s="71"/>
       <c r="N4" s="69" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="O4" s="70"/>
       <c r="P4" s="77"/>
       <c r="Q4" s="69" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R4" s="70"/>
       <c r="S4" s="69" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="T4" s="76"/>
       <c r="U4" s="69" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="V4" s="77"/>
       <c r="X4" s="71"/>
     </row>
     <row r="5" spans="1:24" s="83" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="79" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B5" s="80"/>
       <c r="C5" s="80"/>
@@ -9023,47 +9023,47 @@
     </row>
     <row r="6" spans="1:24" s="92" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="84" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B6" s="85"/>
       <c r="C6" s="86"/>
       <c r="D6" s="87" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E6" s="88" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F6" s="84" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G6" s="88" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="H6" s="86"/>
       <c r="I6" s="90" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="J6" s="88" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="K6" s="85"/>
       <c r="L6" s="85"/>
       <c r="M6" s="86"/>
       <c r="N6" s="88" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="O6" s="85"/>
       <c r="P6" s="86"/>
       <c r="Q6" s="84" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="R6" s="85"/>
       <c r="S6" s="89" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="T6" s="85"/>
       <c r="U6" s="91" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="V6" s="86"/>
       <c r="X6" s="86"/>
@@ -9090,7 +9090,7 @@
     </row>
     <row r="8" spans="1:24" s="92" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="92" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B8" s="80"/>
       <c r="C8" s="80"/>
